--- a/www/Restoration_Monitoring_Cover_EXAMPLE.xlsx
+++ b/www/Restoration_Monitoring_Cover_EXAMPLE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\www\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="8_{31D97D8A-81BF-4130-9925-67CFAF7DC92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1131F112-0661-40A2-9965-DFCB4BEF0F46}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091E1D0F-5C14-4105-B5DC-C387037321C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="22020" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="18870" windowHeight="11265" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -224,9 +224,6 @@
     <t>Stylaster roseus</t>
   </si>
   <si>
-    <t>Tubastraea</t>
-  </si>
-  <si>
     <t>Tubastraea coccinea</t>
   </si>
   <si>
@@ -297,9 +294,6 @@
   </si>
   <si>
     <t>Percent_Cover</t>
-  </si>
-  <si>
-    <t>REQUIRED_Unconsolidated_substrate</t>
   </si>
   <si>
     <t>Cladocora arbuscula</t>
@@ -458,6 +452,12 @@
   </si>
   <si>
     <t>ltoth@usgs.gov</t>
+  </si>
+  <si>
+    <t>REQUIRED Unconsolidated substrate</t>
+  </si>
+  <si>
+    <t>Tubastraea spp.</t>
   </si>
 </sst>
 </file>
@@ -895,22 +895,22 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
@@ -918,52 +918,52 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -992,48 +992,48 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>79</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>80</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>81</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>82</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" t="s">
         <v>83</v>
-      </c>
-      <c r="H1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J1" t="s">
-        <v>101</v>
-      </c>
-      <c r="K1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C2" s="6">
         <v>24.459129999999998</v>
@@ -1042,19 +1042,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J2">
         <v>-1</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C3" s="6">
         <v>24.459129999999998</v>
@@ -1080,19 +1080,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G3">
         <v>100</v>
       </c>
       <c r="H3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C4" s="6">
         <v>24.459129999999998</v>
@@ -1118,19 +1118,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C5" s="6">
         <v>24.459129999999998</v>
@@ -1156,19 +1156,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C6" s="6">
         <v>24.459129999999998</v>
@@ -1194,19 +1194,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G6">
         <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C7" s="6">
         <v>24.459129999999998</v>
@@ -1232,19 +1232,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" s="6">
         <v>24.459129999999998</v>
@@ -1270,19 +1270,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G8">
         <v>100</v>
       </c>
       <c r="H8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J8">
         <v>3</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9" s="6">
         <v>24.459129999999998</v>
@@ -1308,19 +1308,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
       <c r="H9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J9">
         <v>3</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C10" s="6">
         <v>24.459129999999998</v>
@@ -1346,19 +1346,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G10">
         <v>100</v>
       </c>
       <c r="H10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C11" s="6">
         <v>24.459129999999998</v>
@@ -1384,19 +1384,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
       <c r="H11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J11">
         <v>3</v>
@@ -1410,10 +1410,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C12" s="6">
         <v>24.459129999999998</v>
@@ -1422,19 +1422,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G12">
         <v>100</v>
       </c>
       <c r="H12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C13" s="6">
         <v>24.459129999999998</v>
@@ -1460,19 +1460,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G13">
         <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C14" s="6">
         <v>24.459129999999998</v>
@@ -1498,19 +1498,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G14">
         <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C15" s="6">
         <v>24.459129999999998</v>
@@ -1536,19 +1536,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
       <c r="H15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C16" s="6">
         <v>24.459129999999998</v>
@@ -1574,19 +1574,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C17" s="6">
         <v>24.459129999999998</v>
@@ -1612,19 +1612,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G17">
         <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J17">
         <v>10</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C18" s="6">
         <v>24.459129999999998</v>
@@ -1650,19 +1650,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G18">
         <v>100</v>
       </c>
       <c r="H18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C19" s="6">
         <v>24.459129999999998</v>
@@ -1688,19 +1688,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G19">
         <v>100</v>
       </c>
       <c r="H19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J19">
         <v>10</v>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C20" s="6">
         <v>24.459129999999998</v>
@@ -1726,19 +1726,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G20">
         <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C21" s="6">
         <v>24.459129999999998</v>
@@ -1764,19 +1764,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G21">
         <v>100</v>
       </c>
       <c r="H21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J21">
         <v>10</v>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C22" s="6">
         <v>24.459129999999998</v>
@@ -1802,25 +1802,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G22">
         <v>100</v>
       </c>
       <c r="H22" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="L22">
         <v>0.05</v>
@@ -1828,10 +1828,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C23" s="6">
         <v>24.459129999999998</v>
@@ -1840,25 +1840,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G23">
         <v>100</v>
       </c>
       <c r="H23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="L23">
         <v>0.06</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C24" s="6">
         <v>24.459129999999998</v>
@@ -1878,25 +1878,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G24">
         <v>100</v>
       </c>
       <c r="H24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J24">
         <v>3</v>
       </c>
       <c r="K24" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="L24">
         <v>0.5</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C25" s="6">
         <v>24.459129999999998</v>
@@ -1916,25 +1916,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G25">
         <v>100</v>
       </c>
       <c r="H25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J25">
         <v>5</v>
       </c>
       <c r="K25" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="L25">
         <v>0.75</v>
@@ -1942,10 +1942,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C26" s="6">
         <v>24.459129999999998</v>
@@ -1954,25 +1954,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G26">
         <v>100</v>
       </c>
       <c r="H26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J26">
         <v>10</v>
       </c>
       <c r="K26" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="L26">
         <v>0.5</v>
@@ -2000,7 +2000,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4C557318-C684-4454-90B2-DAA9C611E2F1}">
           <x14:formula1>
-            <xm:f>Taxa!A3:A81</xm:f>
+            <xm:f>Taxa!$A$2:A$81</xm:f>
           </x14:formula1>
           <xm:sqref>K2:K1048576</xm:sqref>
         </x14:dataValidation>
@@ -2023,17 +2023,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
@@ -2053,7 +2053,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
@@ -2098,7 +2098,7 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
@@ -2128,7 +2128,7 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
@@ -2163,7 +2163,7 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.45">
@@ -2178,7 +2178,7 @@
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.45">
@@ -2218,7 +2218,7 @@
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.45">
@@ -2258,7 +2258,7 @@
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.45">
@@ -2273,12 +2273,12 @@
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.45">
@@ -2288,7 +2288,7 @@
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.45">
@@ -2308,7 +2308,7 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.45">
@@ -2343,7 +2343,7 @@
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.45">
@@ -2358,7 +2358,7 @@
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.45">
@@ -2373,7 +2373,7 @@
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.45">
@@ -2388,7 +2388,7 @@
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.45">
@@ -2412,13 +2412,13 @@
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A79" s="1" t="s">
-        <v>60</v>
+      <c r="A79" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2434,58 +2434,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2494,6 +2494,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2502,7 +2513,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="647735499ae6baa62e6fc7f5ed3567b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47ff4a2bf1fedf465812d90a21a07c12" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
@@ -2697,18 +2708,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
+    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -2716,7 +2727,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ABA30CC-C1F2-488C-BE05-7ED5EA282AA6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2735,17 +2746,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
-    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="0"/>

--- a/www/Restoration_Monitoring_Cover_EXAMPLE.xlsx
+++ b/www/Restoration_Monitoring_Cover_EXAMPLE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\__git\CBuRT\www\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091E1D0F-5C14-4105-B5DC-C387037321C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E8824E-37D4-48DC-8783-96C6311D60C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="18870" windowHeight="11265" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
+    <workbookView xWindow="2880" yWindow="2880" windowWidth="21600" windowHeight="11333" activeTab="1" xr2:uid="{0278FB9D-D97A-43A8-AA68-A0B70EFAF30B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="118">
   <si>
     <t>Acropora cervicornis</t>
   </si>
@@ -93,18 +93,6 @@
   </si>
   <si>
     <t>Favia fragum</t>
-  </si>
-  <si>
-    <t>Hard Coral (branching)</t>
-  </si>
-  <si>
-    <t>Hard Coral (encrusting)</t>
-  </si>
-  <si>
-    <t>Hard Coral (foliose)</t>
-  </si>
-  <si>
-    <t>Hard Coral (massive)</t>
   </si>
   <si>
     <t>Helioseris cucullata</t>
@@ -895,22 +883,22 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
@@ -918,52 +906,52 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -992,48 +980,48 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
         <v>77</v>
       </c>
-      <c r="B1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>78</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1" t="s">
         <v>79</v>
-      </c>
-      <c r="E1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C2" s="6">
         <v>24.459129999999998</v>
@@ -1042,25 +1030,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J2">
         <v>-1</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L2">
         <v>2.2551546390000001</v>
@@ -1068,10 +1056,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C3" s="6">
         <v>24.459129999999998</v>
@@ -1080,25 +1068,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G3">
         <v>100</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L3">
         <v>2.8799019609999998</v>
@@ -1106,10 +1094,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C4" s="6">
         <v>24.459129999999998</v>
@@ -1118,19 +1106,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1144,10 +1132,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C5" s="6">
         <v>24.459129999999998</v>
@@ -1156,25 +1144,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L5">
         <v>1.481958763</v>
@@ -1182,10 +1170,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C6" s="6">
         <v>24.459129999999998</v>
@@ -1194,25 +1182,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G6">
         <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L6">
         <v>1.3480392160000001</v>
@@ -1220,10 +1208,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C7" s="6">
         <v>24.459129999999998</v>
@@ -1232,19 +1220,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1258,10 +1246,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C8" s="6">
         <v>24.459129999999998</v>
@@ -1270,19 +1258,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G8">
         <v>100</v>
       </c>
       <c r="H8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J8">
         <v>3</v>
@@ -1296,10 +1284,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C9" s="6">
         <v>24.459129999999998</v>
@@ -1308,19 +1296,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J9">
         <v>3</v>
@@ -1334,10 +1322,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C10" s="6">
         <v>24.459129999999998</v>
@@ -1346,25 +1334,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G10">
         <v>100</v>
       </c>
       <c r="H10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J10">
         <v>3</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L10">
         <v>2.95</v>
@@ -1372,10 +1360,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C11" s="6">
         <v>24.459129999999998</v>
@@ -1384,25 +1372,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
       <c r="H11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J11">
         <v>3</v>
       </c>
       <c r="K11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L11">
         <v>1.6</v>
@@ -1410,10 +1398,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C12" s="6">
         <v>24.459129999999998</v>
@@ -1422,19 +1410,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G12">
         <v>100</v>
       </c>
       <c r="H12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1448,10 +1436,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C13" s="6">
         <v>24.459129999999998</v>
@@ -1460,19 +1448,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G13">
         <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1486,10 +1474,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C14" s="6">
         <v>24.459129999999998</v>
@@ -1498,25 +1486,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F14" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G14">
         <v>100</v>
       </c>
       <c r="H14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J14">
         <v>5</v>
       </c>
       <c r="K14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L14">
         <v>2.8</v>
@@ -1524,10 +1512,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C15" s="6">
         <v>24.459129999999998</v>
@@ -1536,25 +1524,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
       <c r="H15" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J15">
         <v>5</v>
       </c>
       <c r="K15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L15">
         <v>1.5</v>
@@ -1562,10 +1550,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C16" s="6">
         <v>24.459129999999998</v>
@@ -1574,25 +1562,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J16">
         <v>5</v>
       </c>
       <c r="K16" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L16">
         <v>0.1</v>
@@ -1600,10 +1588,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C17" s="6">
         <v>24.459129999999998</v>
@@ -1612,19 +1600,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G17">
         <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I17" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J17">
         <v>10</v>
@@ -1638,10 +1626,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C18" s="6">
         <v>24.459129999999998</v>
@@ -1650,19 +1638,19 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G18">
         <v>100</v>
       </c>
       <c r="H18" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I18" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -1676,10 +1664,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C19" s="6">
         <v>24.459129999999998</v>
@@ -1688,25 +1676,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E19" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G19">
         <v>100</v>
       </c>
       <c r="H19" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I19" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J19">
         <v>10</v>
       </c>
       <c r="K19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L19">
         <v>3</v>
@@ -1714,10 +1702,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C20" s="6">
         <v>24.459129999999998</v>
@@ -1726,25 +1714,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G20">
         <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I20" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J20">
         <v>10</v>
       </c>
       <c r="K20" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L20">
         <v>1.9</v>
@@ -1752,10 +1740,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C21" s="6">
         <v>24.459129999999998</v>
@@ -1764,25 +1752,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G21">
         <v>100</v>
       </c>
       <c r="H21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J21">
         <v>10</v>
       </c>
       <c r="K21" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L21">
         <v>0.3</v>
@@ -1790,10 +1778,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C22" s="6">
         <v>24.459129999999998</v>
@@ -1802,25 +1790,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F22" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G22">
         <v>100</v>
       </c>
       <c r="H22" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L22">
         <v>0.05</v>
@@ -1828,10 +1816,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C23" s="6">
         <v>24.459129999999998</v>
@@ -1840,25 +1828,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F23" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G23">
         <v>100</v>
       </c>
       <c r="H23" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I23" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L23">
         <v>0.06</v>
@@ -1866,10 +1854,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C24" s="6">
         <v>24.459129999999998</v>
@@ -1878,25 +1866,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F24" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G24">
         <v>100</v>
       </c>
       <c r="H24" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J24">
         <v>3</v>
       </c>
       <c r="K24" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L24">
         <v>0.5</v>
@@ -1904,10 +1892,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C25" s="6">
         <v>24.459129999999998</v>
@@ -1916,25 +1904,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E25" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F25" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G25">
         <v>100</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J25">
         <v>5</v>
       </c>
       <c r="K25" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L25">
         <v>0.75</v>
@@ -1942,10 +1930,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C26" s="6">
         <v>24.459129999999998</v>
@@ -1954,25 +1942,25 @@
         <v>-81.845830000000007</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G26">
         <v>100</v>
       </c>
       <c r="H26" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I26" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J26">
         <v>10</v>
       </c>
       <c r="K26" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L26">
         <v>0.5</v>
@@ -2000,7 +1988,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4C557318-C684-4454-90B2-DAA9C611E2F1}">
           <x14:formula1>
-            <xm:f>Taxa!$A$2:A$81</xm:f>
+            <xm:f>Taxa!$A$2:A$77</xm:f>
           </x14:formula1>
           <xm:sqref>K2:K1048576</xm:sqref>
         </x14:dataValidation>
@@ -2018,22 +2006,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAEEECA6-441C-430E-B4E3-69F7F23BD6EB}">
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A76"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
@@ -2053,7 +2041,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
@@ -2098,7 +2086,7 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
@@ -2128,7 +2116,7 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
@@ -2143,42 +2131,42 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.45">
@@ -2197,28 +2185,28 @@
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>27</v>
+      <c r="A36" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A40" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.45">
@@ -2238,77 +2226,77 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.45">
@@ -2323,106 +2311,85 @@
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
-        <v>56</v>
+      <c r="A75" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A77" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A78" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A79" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A80" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2434,58 +2401,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2494,26 +2461,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000AA90A7536739341825FB392424435FB" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="647735499ae6baa62e6fc7f5ed3567b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="797e7fd4-719a-42b3-b312-968ffa9058ad" xmlns:ns3="811eef35-9bdd-441e-81aa-50455f68c6c3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47ff4a2bf1fedf465812d90a21a07c12" ns2:_="" ns3:_="">
     <xsd:import namespace="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
@@ -2708,26 +2655,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
-    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="797e7fd4-719a-42b3-b312-968ffa9058ad">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="811eef35-9bdd-441e-81aa-50455f68c6c3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ABA30CC-C1F2-488C-BE05-7ED5EA282AA6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2746,6 +2694,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6BB395-747F-41BC-A23A-168993E4FE92}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9D3406C-31AD-4E38-96F6-B0246BC4EAE6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="797e7fd4-719a-42b3-b312-968ffa9058ad"/>
+    <ds:schemaRef ds:uri="811eef35-9bdd-441e-81aa-50455f68c6c3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{6dd02d64-b7f3-43f7-a145-cfd68d338edf}" enabled="1" method="Standard" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="0"/>
